--- a/backend/wp_templates/F/F1 预付账款.xlsx
+++ b/backend/wp_templates/F/F1 预付账款.xlsx
@@ -20102,7 +20102,7 @@
       <c r="V14" s="281"/>
       <c r="W14" s="281"/>
       <c r="X14" s="280">
-        <f>O14+V14+W14</f>
+        <f>Q14+V14+W14</f>
         <v>0</v>
       </c>
       <c r="Y14" s="277"/>
@@ -20149,7 +20149,7 @@
       <c r="V15" s="281"/>
       <c r="W15" s="281"/>
       <c r="X15" s="280">
-        <f t="shared" ref="X15:X16" si="3">O15+V15+W15</f>
+        <f t="shared" ref="X15:X16" si="3">Q15+V15+W15</f>
         <v>0</v>
       </c>
       <c r="Y15" s="277"/>
@@ -20243,7 +20243,7 @@
       <c r="V17" s="281"/>
       <c r="W17" s="281"/>
       <c r="X17" s="280">
-        <f>O17+V17+W17</f>
+        <f>Q17+V17+W17</f>
         <v>0</v>
       </c>
       <c r="Y17" s="277"/>
@@ -20290,7 +20290,7 @@
       <c r="V18" s="281"/>
       <c r="W18" s="281"/>
       <c r="X18" s="280">
-        <f>O18+V18+W18</f>
+        <f>Q18+V18+W18</f>
         <v>0</v>
       </c>
       <c r="Y18" s="277"/>
@@ -20337,7 +20337,7 @@
       <c r="V19" s="281"/>
       <c r="W19" s="281"/>
       <c r="X19" s="280">
-        <f t="shared" ref="X19" si="5">O19+V19+W19</f>
+        <f t="shared" ref="X19" si="5">Q19+V19+W19</f>
         <v>0</v>
       </c>
       <c r="Y19" s="277"/>
@@ -20384,7 +20384,7 @@
       <c r="V20" s="281"/>
       <c r="W20" s="281"/>
       <c r="X20" s="280">
-        <f>O20+V20+W20</f>
+        <f>Q20+V20+W20</f>
         <v>0</v>
       </c>
       <c r="Y20" s="277"/>
@@ -20431,7 +20431,7 @@
       <c r="V21" s="281"/>
       <c r="W21" s="281"/>
       <c r="X21" s="280">
-        <f>O21+V21+W21</f>
+        <f>Q21+V21+W21</f>
         <v>0</v>
       </c>
       <c r="Y21" s="277"/>
@@ -20478,7 +20478,7 @@
       <c r="V22" s="281"/>
       <c r="W22" s="281"/>
       <c r="X22" s="280">
-        <f>O22+V22+W22</f>
+        <f>Q22+V22+W22</f>
         <v>0</v>
       </c>
       <c r="Y22" s="277"/>
@@ -20523,7 +20523,7 @@
       <c r="V23" s="281"/>
       <c r="W23" s="281"/>
       <c r="X23" s="280">
-        <f t="shared" ref="X23:X34" si="7">O23+V23+W23</f>
+        <f t="shared" ref="X23:X34" si="7">Q23+V23+W23</f>
         <v>0</v>
       </c>
       <c r="Y23" s="277"/>
